--- a/Backend/src/modules/importaciones/plantillas/clientes.xlsx
+++ b/Backend/src/modules/importaciones/plantillas/clientes.xlsx
@@ -5,15 +5,19 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Plantilla" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Instrucciones" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>nombreCompleto</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+  <si>
+    <t>nombres</t>
+  </si>
+  <si>
+    <t>apellidos</t>
   </si>
   <si>
     <t>telefono</t>
@@ -25,35 +29,77 @@
     <t>documentoIdentidad</t>
   </si>
   <si>
-    <t>Juan Perez Garcia</t>
-  </si>
-  <si>
-    <t>987654321</t>
-  </si>
-  <si>
-    <t>Av. Los Pinos 123, San Isidro</t>
-  </si>
-  <si>
-    <t>45678912</t>
-  </si>
-  <si>
-    <t>Maria Lopez Torres</t>
-  </si>
-  <si>
-    <t>912345678</t>
-  </si>
-  <si>
-    <t>Jr. Las Flores 456, Miraflores</t>
-  </si>
-  <si>
-    <t/>
+    <t>Instrucciones — Plantilla de Clientes</t>
+  </si>
+  <si>
+    <t>Reglas generales</t>
+  </si>
+  <si>
+    <t>•  No modifiques los encabezados (primera fila de la hoja "Plantilla").</t>
+  </si>
+  <si>
+    <t>•  No elimines columnas.</t>
+  </si>
+  <si>
+    <t>•  No cambies el orden de las columnas.</t>
+  </si>
+  <si>
+    <t>•  Una fila representa un registro.</t>
+  </si>
+  <si>
+    <t>•  Los registros duplicados seran omitidos automaticamente durante la importacion.</t>
+  </si>
+  <si>
+    <t>•  Al finalizar la importacion podras descargar un reporte con los registros rechazados (fila, motivo y valor recibido).</t>
+  </si>
+  <si>
+    <t>•  No dejes filas completamente vacias entre registros.</t>
+  </si>
+  <si>
+    <t>Campos</t>
+  </si>
+  <si>
+    <t>Campo</t>
+  </si>
+  <si>
+    <t>Obligatorio</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>Nombres del cliente.</t>
+  </si>
+  <si>
+    <t>Apellidos del cliente.</t>
+  </si>
+  <si>
+    <t>Telefono de contacto.</t>
+  </si>
+  <si>
+    <t>Direccion de entrega.</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Documento de identidad (DNI/CE). Si se omite, no se usa para detectar duplicados.</t>
+  </si>
+  <si>
+    <t>Duplicados</t>
+  </si>
+  <si>
+    <t>Se considera duplicado el documento de identidad, cuando se proporciona (dos clientes sin documento no se consideran duplicados entre si).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -63,17 +109,31 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2563EB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -81,13 +141,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,16 +506,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,33 +529,151 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:D21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
